--- a/output/pdf_financials_xlsx/RXM.xlsx
+++ b/output/pdf_financials_xlsx/RXM.xlsx
@@ -1982,13 +1982,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.519637</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>5.519637</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.519637</v>
       </c>
     </row>
     <row r="93">
@@ -2151,13 +2151,13 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.00172</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.001537</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>5.6e-05</v>
       </c>
     </row>
     <row r="104">
@@ -2199,13 +2199,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.262538</v>
+        <v>-0.264258</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.000899</v>
+        <v>0.000638</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.002753</v>
+        <v>0.002809</v>
       </c>
     </row>
     <row r="107">
@@ -2831,7 +2831,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="n">
         <v>0.005047</v>
       </c>
@@ -3032,7 +3036,11 @@
           <t>Share-based payments reserve 9, 10</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>5.519637</v>
       </c>
@@ -3643,7 +3651,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>-0.00172</v>
       </c>

--- a/output/pdf_financials_xlsx/RXM.xlsx
+++ b/output/pdf_financials_xlsx/RXM.xlsx
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.226889</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.226756</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.202175</v>
       </c>
     </row>
     <row r="65">
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.27469</v>
       </c>
     </row>
     <row r="116">
@@ -3742,7 +3742,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
